--- a/reports/tables/comparativa_random_forest.xlsx
+++ b/reports/tables/comparativa_random_forest.xlsx
@@ -617,51 +617,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Random Forest (Class Weight + Sample Weight)</t>
+          <t>Balanced Random Forest Optimizado</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7514</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>0.6944</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0.2961</v>
+        <v>0.6489</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0.9091</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.0851</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5426</v>
+        <v>0.4379</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.6092</v>
+        <v>0.591</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.8128</v>
+        <v>0.8131</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Balanced Random Forest Optimizado</t>
+          <t>Random Forest (Class Weight + Sample Weight)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7028</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0.8199</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.7514</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.2961</v>
       </c>
       <c r="E8" t="n">
-        <v>0.481</v>
+        <v>0.5426</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.6063</v>
+        <v>0.6092</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.8064</v>
+        <v>0.8128</v>
       </c>
     </row>
   </sheetData>
